--- a/Data/EXCEL/Transfer/salemon/20240711/6598-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6598-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E56B6783-9C29-4892-ADA6-6D8BE3E99F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02DF2DBE-FD01-4DD7-B885-6F20810E6121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{AA77CD9C-F0C6-4501-A620-3B9FE9294FBA}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{88A44B1D-5573-49D8-93E4-CDFCFDFDD924}"/>
   </bookViews>
   <sheets>
     <sheet name="6598-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,19 +1261,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0710BC-3D36-436F-9F8A-BCCFCA71B1CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441770C0-C833-429C-96BB-3EC735053E69}">
   <dimension ref="A1:Q189"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1382,7 +1382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>45413</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>45352</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>-1.45</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>45292</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>45231</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>-6.27</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>45170</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>-0.97</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>-0.46</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>45108</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>-3.17</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>-0.37</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>45047</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>44986</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>65.8</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>44927</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>44.3</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>44866</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>44805</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>44743</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>44682</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>-5.29</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>44621</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>-35.5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>-35.5</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>44562</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>-26.8</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>44501</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>44440</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>44378</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>90.6</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>140.4</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>44317</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>98.9</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>44256</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>147.1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>44197</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>189.3</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>185.4</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>44136</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>150.1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>149.69999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>44075</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>103.4</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>146.9</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>44013</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>43952</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>88.9</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>43891</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>97.6</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>43831</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>183.9</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>43770</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>261.8</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>43709</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>284.39999999999998</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>239.8</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>43647</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>200.8</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>156.69999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>43586</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>119.9</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>151.4</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>43525</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>194.1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>158.30000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>43466</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>-69.599999999999994</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>43405</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>-9.65</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>9.08</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>43344</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>-1.55</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>43282</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>42.9</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>82.6</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>43221</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>90.2</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>43160</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>43101</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>345.1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>90.1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>43040</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>147.69999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>88.1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>42979</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>87.1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>90.3</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>42917</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>158.6</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>142.19999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>42856</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>131.6</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>164.4</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>42795</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>173.6</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>-17.7</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>42736</v>
       </c>
@@ -6191,477 +6191,477 @@
         <v>-36.1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>45413</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>45352</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>45292</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>45231</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="9">
         <v>45170</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>45108</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>45047</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
         <v>44986</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="9">
         <v>44927</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>44866</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>44805</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="9">
         <v>44743</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>44682</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>44621</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="9">
         <v>44562</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>44501</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>44440</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>44378</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="9">
         <v>44317</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>44256</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>44136</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="9">
         <v>44075</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="9">
         <v>44013</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="9">
         <v>43952</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="9">
         <v>43891</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="9">
         <v>43831</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>43770</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="9">
         <v>43709</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>43647</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>43586</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="9">
         <v>43525</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="9">
         <v>43466</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="9">
         <v>43405</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>43344</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="9">
         <v>43282</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="9">
         <v>43221</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="9">
         <v>43160</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="9">
         <v>43101</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="9">
         <v>43040</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="9">
         <v>42979</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="9">
         <v>42917</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="9">
         <v>42856</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>42795</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="9">
         <v>42736</v>
       </c>
